--- a/docs/Mapping_casi_uso/unioni_civili/UnCiv_009.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/UnCiv_009.xlsx
@@ -395,7 +395,7 @@
     <t>motivoImpedimentoScritturaConiuge2</t>
   </si>
   <si>
-    <t>Presenza interprete</t>
+    <t>Presenza interprete / soggetto intervenuto</t>
   </si>
   <si>
     <t>ausilioInterprete</t>
